--- a/assessment_forms/043_media_content_distribution_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/043_media_content_distribution_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_3}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 3}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'communications',_'value':_'communications'}</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Communications', 'value': 'Communications'}</t>
+          <t>Communications</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'publishing',_'value':_'publishing'}</t>
+          <t>publishing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Publishing', 'value': 'Publishing'}</t>
+          <t>Publishing</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'publishing',_'value':_'publishing'}</t>
+          <t>publishing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Publishing', 'value': 'Publishing'}</t>
+          <t>Publishing</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_1}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 1}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_3}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 3}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_1}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 1}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_3}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 3}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_3}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 3}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_3}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 3}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'direct_mail',_'value':_'direct_mail'}</t>
+          <t>direct_mail</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Direct Mail', 'value': 'Direct Mail'}</t>
+          <t>Direct Mail</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media', 'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'In-person', 'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'daily',_'value':_1}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Daily', 'value': 1}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_2}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 2}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_3}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 3}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
